--- a/ModelDiscussionGuidelines-CherlukSumdin.xlsx
+++ b/ModelDiscussionGuidelines-CherlukSumdin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mylocal\Documents\ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D57651-647F-495B-B60B-BF612FB793FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C54CD76-17C3-425A-AD85-760ED47DD487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4056" yWindow="1956" windowWidth="17280" windowHeight="8880" xr2:uid="{CAFD73CB-5AE3-43AF-BDB2-5AC34727E82D}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{CAFD73CB-5AE3-43AF-BDB2-5AC34727E82D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">worst = </t>
   </si>
   <si>
-    <t>KNN</t>
+    <t>SVC</t>
   </si>
 </sst>
 </file>
@@ -547,19 +547,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>0.81589999999999996</v>
+        <v>0.81789999999999996</v>
       </c>
       <c r="C4" s="1">
-        <v>0.80730000000000002</v>
+        <v>0.80679999999999996</v>
       </c>
       <c r="D4" s="1">
-        <v>0.66080000000000005</v>
+        <v>0.66839999999999999</v>
       </c>
       <c r="E4" s="1">
-        <v>0.72670000000000001</v>
+        <v>0.73109999999999997</v>
       </c>
       <c r="F4" s="1">
-        <v>0.89549999999999996</v>
+        <v>0.8972</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -567,19 +567,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>0.82469999999999999</v>
+        <v>0.82930000000000004</v>
       </c>
       <c r="C5" s="1">
-        <v>0.78920000000000001</v>
+        <v>0.7984</v>
       </c>
       <c r="D5" s="1">
-        <v>0.71850000000000003</v>
+        <v>0.72130000000000005</v>
       </c>
       <c r="E5" s="1">
-        <v>0.75219999999999998</v>
+        <v>0.75790000000000002</v>
       </c>
       <c r="F5" s="1">
-        <v>0.90790000000000004</v>
+        <v>0.90820000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -587,19 +587,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>0.83499999999999996</v>
+        <v>0.83420000000000005</v>
       </c>
       <c r="C6" s="1">
-        <v>0.9224</v>
+        <v>0.92059999999999997</v>
       </c>
       <c r="D6" s="1">
-        <v>0.60550000000000004</v>
+        <v>0.60460000000000003</v>
       </c>
       <c r="E6" s="1">
-        <v>0.73099999999999998</v>
+        <v>0.72989999999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>0.92789999999999995</v>
+        <v>0.92849999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -607,19 +607,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>0.87250000000000005</v>
+        <v>0.87219999999999998</v>
       </c>
       <c r="C7" s="1">
-        <v>0.85670000000000002</v>
+        <v>0.85460000000000003</v>
       </c>
       <c r="D7" s="1">
-        <v>0.78739999999999999</v>
+        <v>0.78939999999999999</v>
       </c>
       <c r="E7" s="1">
-        <v>0.8206</v>
+        <v>0.82069999999999999</v>
       </c>
       <c r="F7" s="1">
-        <v>0.94750000000000001</v>
+        <v>0.9476</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -627,19 +627,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>0.81779999999999997</v>
+        <v>0.81979999999999997</v>
       </c>
       <c r="C8" s="1">
-        <v>0.77639999999999998</v>
+        <v>0.77969999999999995</v>
       </c>
       <c r="D8" s="1">
-        <v>0.71360000000000001</v>
+        <v>0.71589999999999998</v>
       </c>
       <c r="E8" s="1">
-        <v>0.74370000000000003</v>
+        <v>0.74639999999999995</v>
       </c>
       <c r="F8" s="1">
-        <v>0.89070000000000005</v>
+        <v>0.89270000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -647,19 +647,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>0.84430000000000005</v>
+        <v>0.8155</v>
       </c>
       <c r="C9" s="1">
-        <v>0.85540000000000005</v>
+        <v>0.79759999999999998</v>
       </c>
       <c r="D9" s="1">
-        <v>0.6976</v>
+        <v>0.6724</v>
       </c>
       <c r="E9" s="1">
-        <v>0.76849999999999996</v>
+        <v>0.72970000000000002</v>
       </c>
       <c r="F9" s="1">
-        <v>0.91639999999999999</v>
+        <v>0.89590000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -667,19 +667,19 @@
         <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>0.85770000000000002</v>
+        <v>0.86819999999999997</v>
       </c>
       <c r="C10" s="1">
-        <v>0.87090000000000001</v>
+        <v>0.87109999999999999</v>
       </c>
       <c r="D10" s="1">
-        <v>0.72289999999999999</v>
+        <v>0.75609999999999999</v>
       </c>
       <c r="E10" s="1">
-        <v>0.79</v>
+        <v>0.80959999999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>0.93769999999999998</v>
+        <v>0.94110000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -687,19 +687,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>0.86250000000000004</v>
+        <v>0.87190000000000001</v>
       </c>
       <c r="C11" s="1">
-        <v>0.86680000000000001</v>
+        <v>0.87219999999999998</v>
       </c>
       <c r="D11" s="1">
-        <v>0.74280000000000002</v>
+        <v>0.76639999999999997</v>
       </c>
       <c r="E11" s="1">
-        <v>0.8</v>
+        <v>0.81589999999999996</v>
       </c>
       <c r="F11" s="1">
-        <v>0.94120000000000004</v>
+        <v>0.94440000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
